--- a/scripts/gripic_data.xlsx
+++ b/scripts/gripic_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="66">
   <si>
     <t xml:space="preserve">nom</t>
   </si>
@@ -209,27 +209,6 @@
   </si>
   <si>
     <t xml:space="preserve">content related to Soutenances et journées d'études du GRIPIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collaborations européennes et internationales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rayonnement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">content menu rayonnement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Être invité·e·s au GRIPIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What about us?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Réseaux et expertises</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colabs</t>
   </si>
   <si>
     <t xml:space="preserve">test</t>
@@ -511,7 +490,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="65.52"/>
@@ -906,82 +885,17 @@
         <v>64</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D28" s="0" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="B29" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="B30" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="B32" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="B33" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D33" s="0" t="s">
-        <v>72</v>
-      </c>
-    </row>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/scripts/gripic_data.xlsx
+++ b/scripts/gripic_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="57">
   <si>
     <t xml:space="preserve">nom</t>
   </si>
@@ -151,39 +151,6 @@
     <t xml:space="preserve">content related to Autres</t>
   </si>
   <si>
-    <t xml:space="preserve">Projets en cours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projets de recherche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">content related to Projets en cours</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projets passés</t>
-  </si>
-  <si>
-    <t xml:space="preserve">content related to Projets de recherche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partenariats et participations internes à Sorbonne université</t>
-  </si>
-  <si>
-    <t xml:space="preserve">content related to Partenariats internes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partenariats externes (institutions, entreprises, fondations)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">content related to Partenariats externes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Programmes passés</t>
-  </si>
-  <si>
-    <t xml:space="preserve">content related to Programmes passés : parapluie</t>
-  </si>
-  <si>
     <t xml:space="preserve">Master "Communication en transformation"</t>
   </si>
   <si>
@@ -218,6 +185,12 @@
   </si>
   <si>
     <t xml:space="preserve">gabo papasito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bla bla bla</t>
   </si>
 </sst>
 </file>
@@ -293,8 +266,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -493,404 +470,353 @@
   <dimension ref="A1:D1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="65.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="43.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="33.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="61.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="65.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="33.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="61.91"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="0" t="s">
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="0" t="s">
+      <c r="C4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="C5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="0" t="s">
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="0" t="s">
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="0" t="s">
+      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="0" t="s">
+      <c r="C9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="0" t="s">
+      <c r="C10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="0" t="s">
+      <c r="C11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="0" t="s">
+      <c r="C12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="0" t="s">
+      <c r="C13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="0" t="s">
+      <c r="C14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="0" t="s">
+      <c r="C15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="0" t="s">
+      <c r="C16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="0" t="s">
+      <c r="C17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="0" t="s">
+      <c r="C18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="0" t="s">
+      <c r="C19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="0" t="s">
+      <c r="C20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="0" t="s">
+      <c r="C21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="0" t="s">
+      <c r="C22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>53</v>
       </c>
+      <c r="C23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="B24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D24" s="0" t="s">
+      <c r="B24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="0" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="0" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="0" t="s">
-        <v>65</v>
-      </c>
-    </row>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/scripts/gripic_data.xlsx
+++ b/scripts/gripic_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="68">
   <si>
     <t xml:space="preserve">nom</t>
   </si>
@@ -151,6 +151,39 @@
     <t xml:space="preserve">content related to Autres</t>
   </si>
   <si>
+    <t xml:space="preserve">Projets en cours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projets de recherche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">content related to Projets en cours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projets passés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">content related to Projets de recherche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partenariats et participations internes à Sorbonne université</t>
+  </si>
+  <si>
+    <t xml:space="preserve">content related to Partenariats internes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partenariats externes (institutions, entreprises, fondations)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">content related to Partenariats externes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Programmes passés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">content related to Programmes passés : parapluie</t>
+  </si>
+  <si>
     <t xml:space="preserve">Master "Communication en transformation"</t>
   </si>
   <si>
@@ -187,10 +220,10 @@
     <t xml:space="preserve">gabo papasito</t>
   </si>
   <si>
-    <t xml:space="preserve">Test 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bla bla bla</t>
+    <t xml:space="preserve">vgvkjbkh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a ver </t>
   </si>
 </sst>
 </file>
@@ -789,34 +822,99 @@
         <v>52</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="C24" s="1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/scripts/gripic_data.xlsx
+++ b/scripts/gripic_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="70">
   <si>
     <t xml:space="preserve">nom</t>
   </si>
@@ -224,6 +224,12 @@
   </si>
   <si>
     <t xml:space="preserve">a ver </t>
+  </si>
+  <si>
+    <t xml:space="preserve">gggggg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">otro mas</t>
   </si>
 </sst>
 </file>
@@ -915,6 +921,20 @@
         <v>67</v>
       </c>
     </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
     <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/scripts/gripic_data.xlsx
+++ b/scripts/gripic_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="73">
   <si>
     <t xml:space="preserve">nom</t>
   </si>
@@ -211,6 +211,27 @@
     <t xml:space="preserve">content related to Soutenances et journées d'études du GRIPIC</t>
   </si>
   <si>
+    <t xml:space="preserve">Collaborations européennes et internationales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rayonnement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">content menu rayonnement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Être invité·e·s au GRIPIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What about us?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réseaux et expertises</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colabs</t>
+  </si>
+  <si>
     <t xml:space="preserve">test</t>
   </si>
   <si>
@@ -218,18 +239,6 @@
   </si>
   <si>
     <t xml:space="preserve">gabo papasito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vgvkjbkh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a ver </t>
-  </si>
-  <si>
-    <t xml:space="preserve">gggggg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">otro mas</t>
   </si>
 </sst>
 </file>
@@ -506,7 +515,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D1048576"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="65.52"/>
@@ -901,7 +910,7 @@
         <v>64</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>65</v>
@@ -918,28 +927,65 @@
         <v>6</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="D33" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/scripts/gripic_data.xlsx
+++ b/scripts/gripic_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="75">
   <si>
     <t xml:space="preserve">nom</t>
   </si>
@@ -239,6 +239,12 @@
   </si>
   <si>
     <t xml:space="preserve">gabo papasito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">esta vez si</t>
   </si>
 </sst>
 </file>
@@ -515,7 +521,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="65.52"/>
@@ -986,6 +992,20 @@
         <v>72</v>
       </c>
     </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/scripts/gripic_data.xlsx
+++ b/scripts/gripic_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="70">
   <si>
     <t xml:space="preserve">nom</t>
   </si>
@@ -230,21 +230,6 @@
   </si>
   <si>
     <t xml:space="preserve">Colabs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gabo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gabo papasito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">esta vez si</t>
   </si>
 </sst>
 </file>
@@ -521,7 +506,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="65.52"/>
@@ -978,34 +963,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
